--- a/freeitsm-test-plan-new-suites.xlsx
+++ b/freeitsm-test-plan-new-suites.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -646,6 +646,37 @@
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Fill in Result (Pass / Fail / Blocked / N-A), Tester and Notes as you go.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A note on the Summary sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Its counts are live formulas (COUNTA / COUNTIF) over the suite sheets. They were written</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>without cached values, so Excel computes them the moment you open the file. If a preview tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>shows the Summary as blank or zero, open the workbook in Excel and the figures appear.</t>
         </is>
       </c>
     </row>
